--- a/GameConfig/Datas/_import_v1_preview/叙事物品部件配置表.xlsx
+++ b/GameConfig/Datas/_import_v1_preview/叙事物品部件配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +418,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_camera</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="6">
@@ -615,7 +615,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_camera</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="7">
@@ -644,7 +644,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_glasses</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -656,7 +656,7 @@
         <v>0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_glasses</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="9">
@@ -702,7 +702,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_glasses</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.28</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="10">
@@ -731,7 +731,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_clock</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="18">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22">
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
